--- a/数据表/Datas/ResourcePointConfig_物资点配置.xlsx
+++ b/数据表/Datas/ResourcePointConfig_物资点配置.xlsx
@@ -1,10 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UnityProjects\Seek-Battle-Evacuate\数据表\Datas\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
   <bookViews>
-    <workbookView windowHeight="16660"/>
+    <workbookView windowWidth="24750" windowHeight="12080"/>
   </bookViews>
   <sheets>
     <sheet name="Data" sheetId="1" r:id="rId1"/>
@@ -96,7 +101,7 @@
       <rPr>
         <sz val="12"/>
         <color rgb="FF9C0006"/>
-        <rFont val="PingFang SC Regular"/>
+        <rFont val="微软雅黑"/>
         <charset val="134"/>
       </rPr>
       <t>物资点类型</t>
@@ -105,48 +110,128 @@
       <rPr>
         <sz val="12"/>
         <color rgb="FF9C0006"/>
-        <rFont val="Andale Mono"/>
+        <rFont val="Consolas"/>
         <charset val="134"/>
       </rPr>
       <t>ID</t>
     </r>
   </si>
   <si>
-    <t>显示名</t>
-  </si>
-  <si>
-    <t>难度档位</t>
-  </si>
-  <si>
-    <t>最少生成数量</t>
-  </si>
-  <si>
-    <t>最多生成数量</t>
-  </si>
-  <si>
-    <t>白色权重</t>
-  </si>
-  <si>
-    <t>绿色权重</t>
-  </si>
-  <si>
-    <t>蓝色权重</t>
-  </si>
-  <si>
-    <t>金色权重</t>
-  </si>
-  <si>
-    <t>红色权重</t>
-  </si>
-  <si>
-    <t>实体</t>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF9C0006"/>
+        <rFont val="微软雅黑"/>
+        <charset val="134"/>
+      </rPr>
+      <t>显示名</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF9C0006"/>
+        <rFont val="微软雅黑"/>
+        <charset val="134"/>
+      </rPr>
+      <t>难度档位</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF9C0006"/>
+        <rFont val="微软雅黑"/>
+        <charset val="134"/>
+      </rPr>
+      <t>最少生成数量</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF9C0006"/>
+        <rFont val="微软雅黑"/>
+        <charset val="134"/>
+      </rPr>
+      <t>最多生成数量</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF9C0006"/>
+        <rFont val="微软雅黑"/>
+        <charset val="134"/>
+      </rPr>
+      <t>白色权重</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF9C0006"/>
+        <rFont val="微软雅黑"/>
+        <charset val="134"/>
+      </rPr>
+      <t>绿色权重</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF9C0006"/>
+        <rFont val="微软雅黑"/>
+        <charset val="134"/>
+      </rPr>
+      <t>蓝色权重</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF9C0006"/>
+        <rFont val="微软雅黑"/>
+        <charset val="134"/>
+      </rPr>
+      <t>金色权重</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF9C0006"/>
+        <rFont val="微软雅黑"/>
+        <charset val="134"/>
+      </rPr>
+      <t>红色权重</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF9C0006"/>
+        <rFont val="微软雅黑"/>
+        <charset val="134"/>
+      </rPr>
+      <t>实体</t>
+    </r>
   </si>
   <si>
     <r>
       <rPr>
         <sz val="12"/>
         <color rgb="FF202020"/>
-        <rFont val="PingFang SC Regular"/>
+        <rFont val="微软雅黑"/>
         <charset val="134"/>
       </rPr>
       <t>物资点</t>
@@ -155,7 +240,7 @@
       <rPr>
         <sz val="12"/>
         <color rgb="FF202020"/>
-        <rFont val="Andale Mono"/>
+        <rFont val="Consolas"/>
         <charset val="134"/>
       </rPr>
       <t>1</t>
@@ -178,7 +263,7 @@
       <rPr>
         <sz val="12"/>
         <color rgb="FF202020"/>
-        <rFont val="PingFang SC Regular"/>
+        <rFont val="微软雅黑"/>
         <charset val="134"/>
       </rPr>
       <t>物资点</t>
@@ -187,7 +272,7 @@
       <rPr>
         <sz val="12"/>
         <color rgb="FF202020"/>
-        <rFont val="Andale Mono"/>
+        <rFont val="Consolas"/>
         <charset val="134"/>
       </rPr>
       <t>2</t>
@@ -201,7 +286,7 @@
       <rPr>
         <sz val="12"/>
         <color rgb="FF202020"/>
-        <rFont val="PingFang SC Regular"/>
+        <rFont val="微软雅黑"/>
         <charset val="134"/>
       </rPr>
       <t>物资点</t>
@@ -210,7 +295,7 @@
       <rPr>
         <sz val="12"/>
         <color rgb="FF202020"/>
-        <rFont val="Andale Mono"/>
+        <rFont val="Consolas"/>
         <charset val="134"/>
       </rPr>
       <t>3</t>
@@ -224,7 +309,7 @@
       <rPr>
         <sz val="12"/>
         <color rgb="FF202020"/>
-        <rFont val="PingFang SC Regular"/>
+        <rFont val="微软雅黑"/>
         <charset val="134"/>
       </rPr>
       <t>物资点</t>
@@ -233,7 +318,7 @@
       <rPr>
         <sz val="12"/>
         <color rgb="FF202020"/>
-        <rFont val="Andale Mono"/>
+        <rFont val="Consolas"/>
         <charset val="134"/>
       </rPr>
       <t>4</t>
@@ -247,7 +332,7 @@
       <rPr>
         <sz val="12"/>
         <color rgb="FF202020"/>
-        <rFont val="PingFang SC Regular"/>
+        <rFont val="微软雅黑"/>
         <charset val="134"/>
       </rPr>
       <t>物资点</t>
@@ -256,7 +341,7 @@
       <rPr>
         <sz val="12"/>
         <color rgb="FF202020"/>
-        <rFont val="Andale Mono"/>
+        <rFont val="Consolas"/>
         <charset val="134"/>
       </rPr>
       <t>5</t>
@@ -276,7 +361,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="30">
+  <fonts count="29">
     <font>
       <sz val="11"/>
       <name val="Carlito"/>
@@ -284,55 +369,37 @@
     </font>
     <font>
       <sz val="12"/>
-      <name val="Andale Mono"/>
+      <name val="Consolas"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="12"/>
       <color rgb="FF006100"/>
-      <name val="Andale Mono"/>
+      <name val="Consolas"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="12"/>
       <color rgb="FF1F4E78"/>
-      <name val="Andale Mono"/>
+      <name val="Consolas"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="12"/>
       <color rgb="FF595959"/>
-      <name val="Andale Mono"/>
+      <name val="Consolas"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="12"/>
       <color rgb="FF9C0006"/>
-      <name val="Andale Mono"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="12"/>
-      <color rgb="FF9C0006"/>
-      <name val="PingFang SC Regular"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="12"/>
-      <color rgb="FF9C0006"/>
-      <name val="Carlito"/>
+      <name val="Consolas"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="12"/>
       <color rgb="FF202020"/>
-      <name val="Andale Mono"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="12"/>
-      <color rgb="FF202020"/>
-      <name val="PingFang SC Regular"/>
+      <name val="Consolas"/>
       <charset val="134"/>
     </font>
     <font>
@@ -485,6 +552,18 @@
       <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF202020"/>
+      <name val="微软雅黑"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF9C0006"/>
+      <name val="微软雅黑"/>
+      <charset val="134"/>
     </font>
   </fonts>
   <fills count="35">
@@ -966,19 +1045,31 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="43" fontId="10" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="10" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="10" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="10" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="10" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="13" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -987,132 +1078,120 @@
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="13" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="14" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="14" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="15" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="14" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="14" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="15" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="7" borderId="16" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="8" borderId="17" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="8" borderId="16" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="9" borderId="18" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="19" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="20" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="16" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="17" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="16" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="18" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="19" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="20" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="49"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="49" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="49" applyFont="1" applyAlignment="1">
@@ -1160,22 +1239,16 @@
     <xf numFmtId="0" fontId="5" fillId="5" borderId="11" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="11" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="11" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="11" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="12" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="12" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="12" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="12" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="12" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="12" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="12" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1653,17 +1726,17 @@
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="20" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="10" style="1" customWidth="1"/>
-    <col min="2" max="2" width="15.6838235294118" style="2" customWidth="1"/>
-    <col min="3" max="3" width="13.6029411764706" style="2" customWidth="1"/>
-    <col min="4" max="4" width="20.2132352941176" style="2" customWidth="1"/>
-    <col min="5" max="5" width="16.4191176470588" style="2" customWidth="1"/>
-    <col min="6" max="6" width="13.9705882352941" style="2" customWidth="1"/>
-    <col min="7" max="7" width="15.3161764705882" style="2" customWidth="1"/>
-    <col min="8" max="8" width="18.0147058823529" style="2" customWidth="1"/>
-    <col min="9" max="9" width="16.1691176470588" style="2" customWidth="1"/>
-    <col min="10" max="10" width="13.9705882352941" style="2" customWidth="1"/>
-    <col min="11" max="11" width="15.1985294117647" style="2" customWidth="1"/>
-    <col min="12" max="12" width="28.4264705882353" style="1" customWidth="1"/>
+    <col min="2" max="2" width="15.6833333333333" style="2" customWidth="1"/>
+    <col min="3" max="3" width="13.6" style="2" customWidth="1"/>
+    <col min="4" max="4" width="20.2166666666667" style="2" customWidth="1"/>
+    <col min="5" max="5" width="16.4166666666667" style="2" customWidth="1"/>
+    <col min="6" max="6" width="13.9666666666667" style="2" customWidth="1"/>
+    <col min="7" max="7" width="15.3166666666667" style="2" customWidth="1"/>
+    <col min="8" max="8" width="18.0166666666667" style="2" customWidth="1"/>
+    <col min="9" max="9" width="16.1666666666667" style="2" customWidth="1"/>
+    <col min="10" max="10" width="13.9666666666667" style="2" customWidth="1"/>
+    <col min="11" max="11" width="15.2" style="2" customWidth="1"/>
+    <col min="12" max="12" width="28.425" style="1" customWidth="1"/>
     <col min="13" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
@@ -1793,28 +1866,28 @@
       <c r="C5" s="17" t="s">
         <v>22</v>
       </c>
-      <c r="D5" s="18" t="s">
+      <c r="D5" s="17" t="s">
         <v>23</v>
       </c>
-      <c r="E5" s="18" t="s">
+      <c r="E5" s="17" t="s">
         <v>24</v>
       </c>
-      <c r="F5" s="18" t="s">
+      <c r="F5" s="17" t="s">
         <v>25</v>
       </c>
-      <c r="G5" s="18" t="s">
+      <c r="G5" s="17" t="s">
         <v>26</v>
       </c>
-      <c r="H5" s="18" t="s">
+      <c r="H5" s="17" t="s">
         <v>27</v>
       </c>
-      <c r="I5" s="18" t="s">
+      <c r="I5" s="17" t="s">
         <v>28</v>
       </c>
-      <c r="J5" s="18" t="s">
+      <c r="J5" s="17" t="s">
         <v>29</v>
       </c>
-      <c r="K5" s="18" t="s">
+      <c r="K5" s="17" t="s">
         <v>30</v>
       </c>
       <c r="L5" s="17" t="s">
@@ -1822,14 +1895,14 @@
       </c>
     </row>
     <row r="6" customHeight="1" spans="1:12">
-      <c r="A6" s="19"/>
-      <c r="B6" s="20">
+      <c r="A6" s="18"/>
+      <c r="B6" s="19">
         <v>1</v>
       </c>
-      <c r="C6" s="21" t="s">
+      <c r="C6" s="19" t="s">
         <v>32</v>
       </c>
-      <c r="D6" s="20" t="s">
+      <c r="D6" s="19" t="s">
         <v>33</v>
       </c>
       <c r="E6" s="2">
@@ -1853,15 +1926,15 @@
       <c r="K6" s="2">
         <v>0</v>
       </c>
-      <c r="L6" s="22" t="s">
+      <c r="L6" s="20" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="7" customHeight="1" spans="1:12">
-      <c r="A7" s="19"/>
-      <c r="B7" s="20"/>
-      <c r="C7" s="21"/>
-      <c r="D7" s="20" t="s">
+      <c r="A7" s="18"/>
+      <c r="B7" s="19"/>
+      <c r="C7" s="19"/>
+      <c r="D7" s="19" t="s">
         <v>35</v>
       </c>
       <c r="E7" s="2">
@@ -1887,10 +1960,10 @@
       </c>
     </row>
     <row r="8" customHeight="1" spans="1:12">
-      <c r="A8" s="19"/>
-      <c r="B8" s="20"/>
-      <c r="C8" s="21"/>
-      <c r="D8" s="20" t="s">
+      <c r="A8" s="18"/>
+      <c r="B8" s="19"/>
+      <c r="C8" s="19"/>
+      <c r="D8" s="19" t="s">
         <v>36</v>
       </c>
       <c r="E8" s="2">
@@ -1916,20 +1989,20 @@
       </c>
     </row>
     <row r="9" customHeight="1" spans="1:12">
-      <c r="A9" s="19"/>
-      <c r="B9" s="20"/>
-      <c r="C9" s="21"/>
-      <c r="D9" s="20"/>
+      <c r="A9" s="18"/>
+      <c r="B9" s="19"/>
+      <c r="C9" s="19"/>
+      <c r="D9" s="19"/>
     </row>
     <row r="10" customHeight="1" spans="1:12">
-      <c r="A10" s="19"/>
-      <c r="B10" s="20">
+      <c r="A10" s="18"/>
+      <c r="B10" s="19">
         <v>2</v>
       </c>
-      <c r="C10" s="21" t="s">
+      <c r="C10" s="19" t="s">
         <v>37</v>
       </c>
-      <c r="D10" s="20" t="s">
+      <c r="D10" s="19" t="s">
         <v>33</v>
       </c>
       <c r="E10" s="2">
@@ -1953,15 +2026,15 @@
       <c r="K10" s="2">
         <v>0</v>
       </c>
-      <c r="L10" s="22" t="s">
+      <c r="L10" s="20" t="s">
         <v>38</v>
       </c>
     </row>
     <row r="11" customHeight="1" spans="1:12">
-      <c r="A11" s="19"/>
-      <c r="B11" s="20"/>
-      <c r="C11" s="21"/>
-      <c r="D11" s="20" t="s">
+      <c r="A11" s="18"/>
+      <c r="B11" s="19"/>
+      <c r="C11" s="19"/>
+      <c r="D11" s="19" t="s">
         <v>35</v>
       </c>
       <c r="E11" s="2">
@@ -1987,10 +2060,10 @@
       </c>
     </row>
     <row r="12" customHeight="1" spans="1:12">
-      <c r="A12" s="19"/>
-      <c r="B12" s="20"/>
-      <c r="C12" s="21"/>
-      <c r="D12" s="20" t="s">
+      <c r="A12" s="18"/>
+      <c r="B12" s="19"/>
+      <c r="C12" s="19"/>
+      <c r="D12" s="19" t="s">
         <v>36</v>
       </c>
       <c r="E12" s="2">
@@ -2016,20 +2089,20 @@
       </c>
     </row>
     <row r="13" customHeight="1" spans="1:12">
-      <c r="A13" s="19"/>
-      <c r="B13" s="20"/>
-      <c r="C13" s="21"/>
-      <c r="D13" s="20"/>
+      <c r="A13" s="18"/>
+      <c r="B13" s="19"/>
+      <c r="C13" s="19"/>
+      <c r="D13" s="19"/>
     </row>
     <row r="14" customHeight="1" spans="1:12">
-      <c r="A14" s="19"/>
-      <c r="B14" s="20">
+      <c r="A14" s="18"/>
+      <c r="B14" s="19">
         <v>3</v>
       </c>
-      <c r="C14" s="21" t="s">
+      <c r="C14" s="19" t="s">
         <v>39</v>
       </c>
-      <c r="D14" s="20" t="s">
+      <c r="D14" s="19" t="s">
         <v>33</v>
       </c>
       <c r="E14" s="2">
@@ -2053,15 +2126,15 @@
       <c r="K14" s="2">
         <v>0</v>
       </c>
-      <c r="L14" s="22" t="s">
+      <c r="L14" s="20" t="s">
         <v>40</v>
       </c>
     </row>
     <row r="15" customHeight="1" spans="1:12">
-      <c r="A15" s="19"/>
-      <c r="B15" s="20"/>
-      <c r="C15" s="21"/>
-      <c r="D15" s="20" t="s">
+      <c r="A15" s="18"/>
+      <c r="B15" s="19"/>
+      <c r="C15" s="19"/>
+      <c r="D15" s="19" t="s">
         <v>35</v>
       </c>
       <c r="E15" s="2">
@@ -2087,10 +2160,10 @@
       </c>
     </row>
     <row r="16" customHeight="1" spans="1:12">
-      <c r="A16" s="19"/>
-      <c r="B16" s="20"/>
-      <c r="C16" s="21"/>
-      <c r="D16" s="20" t="s">
+      <c r="A16" s="18"/>
+      <c r="B16" s="19"/>
+      <c r="C16" s="19"/>
+      <c r="D16" s="19" t="s">
         <v>36</v>
       </c>
       <c r="E16" s="2">
@@ -2116,20 +2189,20 @@
       </c>
     </row>
     <row r="17" customHeight="1" spans="1:12">
-      <c r="A17" s="19"/>
-      <c r="B17" s="20"/>
-      <c r="C17" s="21"/>
-      <c r="D17" s="20"/>
+      <c r="A17" s="18"/>
+      <c r="B17" s="19"/>
+      <c r="C17" s="19"/>
+      <c r="D17" s="19"/>
     </row>
     <row r="18" customHeight="1" spans="1:12">
-      <c r="A18" s="19"/>
-      <c r="B18" s="20">
+      <c r="A18" s="18"/>
+      <c r="B18" s="19">
         <v>4</v>
       </c>
-      <c r="C18" s="21" t="s">
+      <c r="C18" s="19" t="s">
         <v>41</v>
       </c>
-      <c r="D18" s="20" t="s">
+      <c r="D18" s="19" t="s">
         <v>33</v>
       </c>
       <c r="E18" s="2">
@@ -2153,15 +2226,15 @@
       <c r="K18" s="2">
         <v>0</v>
       </c>
-      <c r="L18" s="22" t="s">
+      <c r="L18" s="20" t="s">
         <v>42</v>
       </c>
     </row>
     <row r="19" customHeight="1" spans="1:12">
-      <c r="A19" s="19"/>
-      <c r="B19" s="20"/>
-      <c r="C19" s="21"/>
-      <c r="D19" s="20" t="s">
+      <c r="A19" s="18"/>
+      <c r="B19" s="19"/>
+      <c r="C19" s="19"/>
+      <c r="D19" s="19" t="s">
         <v>35</v>
       </c>
       <c r="E19" s="2">
@@ -2187,10 +2260,10 @@
       </c>
     </row>
     <row r="20" customHeight="1" spans="1:12">
-      <c r="A20" s="19"/>
-      <c r="B20" s="20"/>
-      <c r="C20" s="21"/>
-      <c r="D20" s="20" t="s">
+      <c r="A20" s="18"/>
+      <c r="B20" s="19"/>
+      <c r="C20" s="19"/>
+      <c r="D20" s="19" t="s">
         <v>36</v>
       </c>
       <c r="E20" s="2">
@@ -2216,20 +2289,20 @@
       </c>
     </row>
     <row r="21" customHeight="1" spans="1:12">
-      <c r="A21" s="19"/>
-      <c r="B21" s="20"/>
-      <c r="C21" s="21"/>
-      <c r="D21" s="20"/>
+      <c r="A21" s="18"/>
+      <c r="B21" s="19"/>
+      <c r="C21" s="19"/>
+      <c r="D21" s="19"/>
     </row>
     <row r="22" customHeight="1" spans="1:12">
-      <c r="A22" s="19"/>
-      <c r="B22" s="20">
+      <c r="A22" s="18"/>
+      <c r="B22" s="19">
         <v>5</v>
       </c>
-      <c r="C22" s="21" t="s">
+      <c r="C22" s="19" t="s">
         <v>43</v>
       </c>
-      <c r="D22" s="20" t="s">
+      <c r="D22" s="19" t="s">
         <v>33</v>
       </c>
       <c r="E22" s="2">
@@ -2253,7 +2326,7 @@
       <c r="K22" s="2">
         <v>2</v>
       </c>
-      <c r="L22" s="22" t="s">
+      <c r="L22" s="20" t="s">
         <v>44</v>
       </c>
     </row>

--- a/数据表/Datas/ResourcePointConfig_物资点配置.xlsx
+++ b/数据表/Datas/ResourcePointConfig_物资点配置.xlsx
@@ -555,13 +555,13 @@
     </font>
     <font>
       <sz val="12"/>
-      <color rgb="FF202020"/>
+      <color rgb="FF9C0006"/>
       <name val="微软雅黑"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="12"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FF202020"/>
       <name val="微软雅黑"/>
       <charset val="134"/>
     </font>
